--- a/outputs/341-14.xlsx
+++ b/outputs/341-14.xlsx
@@ -248,52 +248,56 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -731,124 +735,124 @@
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="n">
+      <c r="B1" s="9" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="9" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="9" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="9" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="9" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="9" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="11" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="9" t="n">
         <v>710</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <v>730</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="1" t="n">
@@ -856,7 +860,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="1" t="n">
@@ -864,12 +868,12 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="1" t="n">
@@ -877,7 +881,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="1" t="n">
@@ -885,7 +889,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B20" s="1" t="n">
@@ -893,7 +897,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B21" s="1" t="n">
@@ -901,7 +905,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="1" t="n">
@@ -909,7 +913,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="1" t="n">
@@ -917,7 +921,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="1" t="n">
@@ -925,7 +929,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B25" s="1" t="n">
@@ -933,7 +937,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="1" t="n">
@@ -941,7 +945,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B27" s="1" t="n">
@@ -949,7 +953,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="1" t="n">

--- a/outputs/341-14.xlsx
+++ b/outputs/341-14.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="24">
   <si>
     <t xml:space="preserve">A</t>
   </si>
@@ -96,6 +96,21 @@
   </si>
   <si>
     <t xml:space="preserve">321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">730</t>
   </si>
 </sst>
 </file>
@@ -248,57 +263,61 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -732,232 +751,139 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="n">
-        <v>100</v>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="n">
-        <v>200</v>
+      <c r="B2" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="9" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="B4" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="B6" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>800</v>
+      <c r="B8" s="8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>300</v>
+        <v>9</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="11" t="n">
-        <v>400</v>
+      <c r="B10" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>500</v>
+        <v>11</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>600</v>
+      <c r="B12" s="11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>710</v>
+        <v>13</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>250</v>
+      <c r="B14" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
+      <c r="A17" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>321</v>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
